--- a/SAULink9_PartList_ATPI.xlsx
+++ b/SAULink9_PartList_ATPI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HAM\DIY\SVXLink\SAULink9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95086701-90CD-44C6-B6DE-06F9FDDB3410}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01664DA9-D098-4D8F-A0CB-597EA1E08BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{323B2ECF-0824-4216-B6CD-CF298D8265A9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{323B2ECF-0824-4216-B6CD-CF298D8265A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -625,14 +625,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F289346-AD84-47FC-8861-EA845A807292}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="68.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="114.85546875" customWidth="1"/>
+    <col min="1" max="1" width="68.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="114.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -643,7 +643,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>26</v>
       </c>
@@ -654,7 +654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
@@ -663,7 +663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -674,7 +674,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -685,7 +685,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
@@ -696,7 +696,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -707,7 +707,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -718,7 +718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -729,7 +729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -740,7 +740,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -751,7 +751,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -762,7 +762,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
@@ -773,30 +773,30 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B14" s="4">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="4"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="4"/>
       <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -807,7 +807,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
@@ -818,7 +818,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
@@ -829,7 +829,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
@@ -840,7 +840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -851,7 +851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
@@ -862,7 +862,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>38</v>
       </c>
@@ -871,7 +871,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
@@ -880,7 +880,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>41</v>
       </c>
@@ -889,15 +889,15 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
       <c r="C26" s="11"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B27" s="8">
         <f>SUM(B2:B25)</f>
-        <v>115.63</v>
+        <v>116.13</v>
       </c>
     </row>
   </sheetData>

--- a/SAULink9_PartList_ATPI.xlsx
+++ b/SAULink9_PartList_ATPI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HAM\DIY\SVXLink\SAULink9\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\Eigene Dateien\HAM\DIY\SAULink9\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01664DA9-D098-4D8F-A0CB-597EA1E08BA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F248B85-5544-4D3E-BCF4-6A25AF2BE3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{323B2ECF-0824-4216-B6CD-CF298D8265A9}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{323B2ECF-0824-4216-B6CD-CF298D8265A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -625,14 +625,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F289346-AD84-47FC-8861-EA845A807292}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="68.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.109375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="114.88671875" customWidth="1"/>
+    <col min="1" max="1" width="68.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="114.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -643,18 +643,18 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="4">
-        <v>20.56</v>
+        <v>22.58</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
@@ -663,7 +663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -674,7 +674,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -685,7 +685,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>39</v>
       </c>
@@ -696,7 +696,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>32</v>
       </c>
@@ -707,7 +707,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -718,7 +718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -729,7 +729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>42</v>
       </c>
@@ -740,7 +740,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -751,7 +751,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -762,7 +762,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
@@ -773,7 +773,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>36</v>
       </c>
@@ -784,19 +784,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="4"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="4"/>
       <c r="C16" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>7</v>
       </c>
@@ -807,7 +807,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
@@ -818,7 +818,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>14</v>
       </c>
@@ -829,7 +829,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>16</v>
       </c>
@@ -840,7 +840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -851,7 +851,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
@@ -862,7 +862,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>38</v>
       </c>
@@ -871,7 +871,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
@@ -880,7 +880,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>41</v>
       </c>
@@ -889,15 +889,15 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="12"/>
       <c r="C26" s="11"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B27" s="8">
         <f>SUM(B2:B25)</f>
-        <v>116.13</v>
+        <v>118.14999999999999</v>
       </c>
     </row>
   </sheetData>
